--- a/cp-upgrade-mhd/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-upgrade-mhd/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:39:30+00:00</t>
+    <t>2026-05-05T15:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -987,7 +987,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1144,9 +1144,6 @@
   </si>
   <si>
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1482,7 +1479,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1631,7 +1628,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -6512,7 +6509,7 @@
         <v>152</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>360</v>
+        <v>153</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6542,36 +6539,36 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AK37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6597,10 +6594,10 @@
         <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6651,7 +6648,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6669,10 +6666,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6686,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6810,10 +6807,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6933,10 +6930,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7058,10 +7055,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7084,13 +7081,13 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7141,7 +7138,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7159,30 +7156,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7300,10 +7297,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7423,10 +7420,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7452,14 +7449,14 @@
         <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7472,7 +7469,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7487,28 +7484,28 @@
         <v>224</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7529,16 +7526,16 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7546,10 +7543,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7575,14 +7572,14 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7595,7 +7592,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7631,7 +7628,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7652,7 +7649,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7669,10 +7666,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7695,19 +7692,19 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7756,7 +7753,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7777,16 +7774,16 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7794,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7820,19 +7817,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7845,43 +7842,43 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7902,16 +7899,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7919,10 +7916,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7945,19 +7942,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8006,7 +8003,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8027,7 +8024,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8044,10 +8041,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8070,19 +8067,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8128,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8152,7 +8149,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8169,10 +8166,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8198,14 +8195,14 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8218,43 +8215,43 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8275,7 +8272,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8292,10 +8289,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8318,17 +8315,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8377,7 +8374,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8398,7 +8395,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8415,10 +8412,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8444,13 +8441,13 @@
         <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8480,7 +8477,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8498,7 +8495,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8510,36 +8507,36 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AK53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>457</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8565,13 +8562,13 @@
         <v>316</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8621,7 +8618,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8642,7 +8639,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8659,10 +8656,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8780,10 +8777,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8903,10 +8900,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9028,10 +9025,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9054,13 +9051,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9111,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9126,19 +9123,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9149,10 +9146,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9178,13 +9175,13 @@
         <v>242</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9213,11 +9210,11 @@
         <v>159</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9234,7 +9231,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9246,36 +9243,36 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AK59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9298,13 +9295,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9355,7 +9352,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9373,30 +9370,30 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9422,10 +9419,10 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9456,7 +9453,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9474,7 +9471,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9486,36 +9483,36 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9541,16 +9538,16 @@
         <v>242</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9579,7 +9576,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9597,7 +9594,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9609,19 +9606,19 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9630,15 +9627,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9664,10 +9661,10 @@
         <v>267</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9718,7 +9715,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9751,15 +9748,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9782,16 +9779,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9841,7 +9838,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9859,22 +9856,22 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
   </sheetData>
